--- a/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>出库单号</t>
   </si>
@@ -47,6 +47,9 @@
     <t>单据类型</t>
   </si>
   <si>
+    <t>销售平台</t>
+  </si>
+  <si>
     <t>单据状态</t>
   </si>
   <si>
@@ -63,6 +66,9 @@
   </si>
   <si>
     <t>销售员</t>
+  </si>
+  <si>
+    <t>销售部门</t>
   </si>
   <si>
     <t>库存组织</t>
@@ -172,6 +178,9 @@
     <t>{.orderTypeName}</t>
   </si>
   <si>
+    <t>{.dictPlatform}</t>
+  </si>
+  <si>
     <t>{.approveStatusName}</t>
   </si>
   <si>
@@ -188,6 +197,9 @@
   </si>
   <si>
     <t>{.sellerName}</t>
+  </si>
+  <si>
+    <t>{.salesDeptName}</t>
   </si>
   <si>
     <t>{.warehouseOrgName}</t>
@@ -997,17 +1009,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1331,28 +1343,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF9"/>
+  <dimension ref="A1:AH9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="14.25" customWidth="1"/>
     <col min="3" max="4" width="18.25" customWidth="1"/>
     <col min="5" max="5" width="20.125" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="18.125" customWidth="1"/>
-    <col min="9" max="14" width="30.625" customWidth="1"/>
-    <col min="15" max="15" width="14.75" customWidth="1"/>
-    <col min="16" max="21" width="27" customWidth="1"/>
-    <col min="22" max="23" width="15.125" customWidth="1"/>
-    <col min="24" max="24" width="11.875" customWidth="1"/>
-    <col min="25" max="25" width="25.625" customWidth="1"/>
-    <col min="26" max="26" width="21.25" customWidth="1"/>
-    <col min="27" max="28" width="21.125" customWidth="1"/>
-    <col min="29" max="29" width="21" customWidth="1"/>
-    <col min="30" max="32" width="20.625" customWidth="1"/>
+    <col min="7" max="8" width="17.5" customWidth="1"/>
+    <col min="9" max="9" width="18.125" customWidth="1"/>
+    <col min="10" max="16" width="30.625" customWidth="1"/>
+    <col min="17" max="17" width="14.75" customWidth="1"/>
+    <col min="18" max="23" width="27" customWidth="1"/>
+    <col min="24" max="25" width="15.125" customWidth="1"/>
+    <col min="26" max="26" width="11.875" customWidth="1"/>
+    <col min="27" max="27" width="25.625" customWidth="1"/>
+    <col min="28" max="28" width="21.25" customWidth="1"/>
+    <col min="29" max="30" width="21.125" customWidth="1"/>
+    <col min="31" max="31" width="21" customWidth="1"/>
+    <col min="32" max="34" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1449,119 +1461,131 @@
       <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:34">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="X2" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="4" spans="8:8">
-      <c r="H4" s="2"/>
+    <row r="4" spans="9:9">
+      <c r="I4" s="5"/>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
@@ -178,7 +178,7 @@
     <t>{.orderTypeName}</t>
   </si>
   <si>
-    <t>{.dictPlatform}</t>
+    <t>{.dictPlatformName}</t>
   </si>
   <si>
     <t>{.approveStatusName}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
@@ -178,7 +178,7 @@
     <t>{.orderTypeName}</t>
   </si>
   <si>
-    <t>{.dictPlatformName}</t>
+    <t>{.dictPlatform}</t>
   </si>
   <si>
     <t>{.approveStatusName}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
   <si>
     <t>出库单号</t>
   </si>
@@ -1343,7 +1343,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH9"/>
+  <dimension ref="A1:AJ9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="14.25" customWidth="1"/>
@@ -1358,13 +1358,13 @@
     <col min="24" max="25" width="15.125" customWidth="1"/>
     <col min="26" max="26" width="11.875" customWidth="1"/>
     <col min="27" max="27" width="25.625" customWidth="1"/>
-    <col min="28" max="28" width="21.25" customWidth="1"/>
-    <col min="29" max="30" width="21.125" customWidth="1"/>
-    <col min="31" max="31" width="21" customWidth="1"/>
-    <col min="32" max="34" width="20.625" customWidth="1"/>
+    <col min="28" max="30" width="21.25" customWidth="1"/>
+    <col min="31" max="32" width="21.125" customWidth="1"/>
+    <col min="33" max="33" width="21" customWidth="1"/>
+    <col min="34" max="36" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:36">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1447,28 +1447,34 @@
         <v>26</v>
       </c>
       <c r="AB1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:36">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
@@ -1551,24 +1557,30 @@
         <v>60</v>
       </c>
       <c r="AB2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>67</v>
       </c>
     </row>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
   <si>
     <t>出库单号</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>出货仓库</t>
+  </si>
+  <si>
+    <t>虚拟仓</t>
   </si>
   <si>
     <t>出库日期</t>
@@ -297,6 +300,9 @@
       </rPr>
       <t>}</t>
     </r>
+  </si>
+  <si>
+    <t>{.virtualWarehouseName}</t>
   </si>
   <si>
     <t>{.billDate}</t>
@@ -1343,7 +1349,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ9"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="14.25" customWidth="1"/>
@@ -1357,14 +1363,14 @@
     <col min="18" max="23" width="27" customWidth="1"/>
     <col min="24" max="25" width="15.125" customWidth="1"/>
     <col min="26" max="26" width="11.875" customWidth="1"/>
-    <col min="27" max="27" width="25.625" customWidth="1"/>
-    <col min="28" max="30" width="21.25" customWidth="1"/>
-    <col min="31" max="32" width="21.125" customWidth="1"/>
-    <col min="33" max="33" width="21" customWidth="1"/>
-    <col min="34" max="36" width="20.625" customWidth="1"/>
+    <col min="27" max="28" width="25.625" customWidth="1"/>
+    <col min="29" max="31" width="21.25" customWidth="1"/>
+    <col min="32" max="33" width="21.125" customWidth="1"/>
+    <col min="34" max="34" width="21" customWidth="1"/>
+    <col min="35" max="37" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36">
+    <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1447,13 +1453,13 @@
         <v>26</v>
       </c>
       <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>28</v>
@@ -1473,115 +1479,121 @@
       <c r="AJ1" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="AK1" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="2" spans="1:36">
+    <row r="2" spans="1:37">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Z2" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="AC2" s="1" t="s">
         <v>49</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="9:9">

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
   <si>
     <t>出库单号</t>
   </si>
@@ -126,6 +126,15 @@
   </si>
   <si>
     <t>审核人</t>
+  </si>
+  <si>
+    <t>单据备注</t>
+  </si>
+  <si>
+    <t>明细备注</t>
+  </si>
+  <si>
+    <t>客户备注</t>
   </si>
   <si>
     <t>创建人</t>
@@ -337,6 +346,15 @@
   </si>
   <si>
     <t>{.approveUserName}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.detailRemark}</t>
+  </si>
+  <si>
+    <t>{.customerRemark}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1349,7 +1367,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK9"/>
+  <dimension ref="A1:AN9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="14.25" customWidth="1"/>
@@ -1367,10 +1385,10 @@
     <col min="29" max="31" width="21.25" customWidth="1"/>
     <col min="32" max="33" width="21.125" customWidth="1"/>
     <col min="34" max="34" width="21" customWidth="1"/>
-    <col min="35" max="37" width="20.625" customWidth="1"/>
+    <col min="35" max="40" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:40">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1482,118 +1500,136 @@
       <c r="AK1" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="AL1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:40">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="R2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="AE2" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN2" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="9:9">

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="72">
   <si>
     <t>出库单号</t>
   </si>
@@ -38,6 +38,9 @@
     <t>销售单号</t>
   </si>
   <si>
+    <t>平台订单号</t>
+  </si>
+  <si>
     <t>第三方单据编号</t>
   </si>
   <si>
@@ -141,6 +144,9 @@
   </si>
   <si>
     <t>{.soCode}</t>
+  </si>
+  <si>
+    <t>{.platformCode}</t>
   </si>
   <si>
     <t>{.thirdCode}</t>
@@ -1349,28 +1355,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK9"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="14.25" customWidth="1"/>
-    <col min="3" max="4" width="18.25" customWidth="1"/>
-    <col min="5" max="5" width="20.125" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="8" width="17.5" customWidth="1"/>
-    <col min="9" max="9" width="18.125" customWidth="1"/>
-    <col min="10" max="16" width="30.625" customWidth="1"/>
-    <col min="17" max="17" width="14.75" customWidth="1"/>
-    <col min="18" max="23" width="27" customWidth="1"/>
-    <col min="24" max="25" width="15.125" customWidth="1"/>
-    <col min="26" max="26" width="11.875" customWidth="1"/>
-    <col min="27" max="28" width="25.625" customWidth="1"/>
-    <col min="29" max="31" width="21.25" customWidth="1"/>
-    <col min="32" max="33" width="21.125" customWidth="1"/>
-    <col min="34" max="34" width="21" customWidth="1"/>
-    <col min="35" max="37" width="20.625" customWidth="1"/>
+    <col min="3" max="5" width="18.25" customWidth="1"/>
+    <col min="6" max="6" width="20.125" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="9" width="17.5" customWidth="1"/>
+    <col min="10" max="10" width="18.125" customWidth="1"/>
+    <col min="11" max="17" width="30.625" customWidth="1"/>
+    <col min="18" max="18" width="14.75" customWidth="1"/>
+    <col min="19" max="24" width="27" customWidth="1"/>
+    <col min="25" max="26" width="15.125" customWidth="1"/>
+    <col min="27" max="27" width="11.875" customWidth="1"/>
+    <col min="28" max="29" width="25.625" customWidth="1"/>
+    <col min="30" max="32" width="21.25" customWidth="1"/>
+    <col min="33" max="34" width="21.125" customWidth="1"/>
+    <col min="35" max="35" width="21" customWidth="1"/>
+    <col min="36" max="38" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1456,13 +1462,13 @@
         <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>29</v>
@@ -1482,122 +1488,128 @@
       <c r="AK1" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="AL1" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:38">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="AF2" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="4" spans="9:9">
-      <c r="I4" s="5"/>
+    <row r="4" spans="10:10">
+      <c r="J4" s="5"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="78">
   <si>
     <t>出库单号</t>
   </si>
@@ -38,6 +38,9 @@
     <t>销售单号</t>
   </si>
   <si>
+    <t>平台订单号</t>
+  </si>
+  <si>
     <t>第三方单据编号</t>
   </si>
   <si>
@@ -150,6 +153,9 @@
   </si>
   <si>
     <t>{.soCode}</t>
+  </si>
+  <si>
+    <t>{.platformCode}</t>
   </si>
   <si>
     <t>{.thirdCode}</t>
@@ -1367,28 +1373,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AN9"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="14.25" customWidth="1"/>
-    <col min="3" max="4" width="18.25" customWidth="1"/>
-    <col min="5" max="5" width="20.125" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="8" width="17.5" customWidth="1"/>
-    <col min="9" max="9" width="18.125" customWidth="1"/>
-    <col min="10" max="16" width="30.625" customWidth="1"/>
-    <col min="17" max="17" width="14.75" customWidth="1"/>
-    <col min="18" max="23" width="27" customWidth="1"/>
-    <col min="24" max="25" width="15.125" customWidth="1"/>
-    <col min="26" max="26" width="11.875" customWidth="1"/>
-    <col min="27" max="28" width="25.625" customWidth="1"/>
-    <col min="29" max="31" width="21.25" customWidth="1"/>
-    <col min="32" max="33" width="21.125" customWidth="1"/>
-    <col min="34" max="34" width="21" customWidth="1"/>
-    <col min="35" max="40" width="20.625" customWidth="1"/>
+    <col min="3" max="5" width="18.25" customWidth="1"/>
+    <col min="6" max="6" width="20.125" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+    <col min="8" max="9" width="17.5" customWidth="1"/>
+    <col min="10" max="10" width="18.125" customWidth="1"/>
+    <col min="11" max="17" width="30.625" customWidth="1"/>
+    <col min="18" max="18" width="14.75" customWidth="1"/>
+    <col min="19" max="24" width="27" customWidth="1"/>
+    <col min="25" max="26" width="15.125" customWidth="1"/>
+    <col min="27" max="27" width="11.875" customWidth="1"/>
+    <col min="28" max="29" width="25.625" customWidth="1"/>
+    <col min="30" max="32" width="21.25" customWidth="1"/>
+    <col min="33" max="34" width="21.125" customWidth="1"/>
+    <col min="35" max="35" width="21" customWidth="1"/>
+    <col min="36" max="41" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1474,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>29</v>
@@ -1509,131 +1515,137 @@
       <c r="AN1" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="AO1" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="A2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="AF2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="AO2" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="4" spans="9:9">
-      <c r="I4" s="5"/>
+    <row r="4" spans="10:10">
+      <c r="J4" s="5"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/soOutstock.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="80">
   <si>
     <t>出库单号</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>客户备注</t>
+  </si>
+  <si>
+    <t>客户PO</t>
   </si>
   <si>
     <t>创建人</t>
@@ -361,6 +364,9 @@
   </si>
   <si>
     <t>{.customerRemark}</t>
+  </si>
+  <si>
+    <t>{.customerPO}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1373,7 +1379,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO9"/>
+  <dimension ref="A1:AP9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="14.25" customWidth="1"/>
@@ -1391,10 +1397,10 @@
     <col min="30" max="32" width="21.25" customWidth="1"/>
     <col min="33" max="34" width="21.125" customWidth="1"/>
     <col min="35" max="35" width="21" customWidth="1"/>
-    <col min="36" max="41" width="20.625" customWidth="1"/>
+    <col min="36" max="42" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41">
+    <row r="1" spans="1:42">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1518,130 +1524,136 @@
       <c r="AO1" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="AP1" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:42">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA2" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="AF2" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="10:10">
